--- a/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>22.1</v>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>21.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>22.3</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>21.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>20.7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>20.5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Avg_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -413,8 +410,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>22.1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +424,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>22.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -554,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -609,8 +606,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>22.3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -624,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -652,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -680,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -708,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -792,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Avg_Temperature_timeseries.xlsx
@@ -425,7 +425,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
